--- a/samples/ss_ngimbang_ingest.xlsx
+++ b/samples/ss_ngimbang_ingest.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/samples/ss_ngimbang_ingest.xlsx
+++ b/samples/ss_ngimbang_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 1,2 Ngimbang 500/150 kV</t>
+          <t>IBT 1 Ngimbang 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -738,31 +734,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ngimbang (bus 150 kV)</t>
+          <t>IBT 2 Ngimbang 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>IBT 2 NBANG7</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NBANG7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>NBANG5</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -774,10 +784,14 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -791,12 +805,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tuban Jawa</t>
+          <t>Ngimbang (bus 150 kV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TJWAR</t>
+          <t>NBANG5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -844,17 +858,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLTU Tuban Jawa</t>
+          <t>Tuban Jawa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KIT_TJWAR</t>
+          <t>TJWAR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -897,21 +911,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jatidondong</t>
+          <t>PLTU Tuban Jawa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JDONG</t>
+          <t>KIT_TJWAR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -950,12 +964,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Babat</t>
+          <t>Jatidondong</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BABAT</t>
+          <t>JDONG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1003,12 +1017,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Merakurak/Mwang</t>
+          <t>Babat</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MWANG</t>
+          <t>BABAT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1056,12 +1070,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tuban</t>
+          <t>Merakurak/Mwang</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TUBAN</t>
+          <t>MWANG</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1092,14 +1106,10 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1113,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cendang</t>
+          <t>Tuban</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CDANG</t>
+          <t>TUBAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1127,7 +1137,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1149,10 +1159,14 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1166,12 +1180,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jombang</t>
+          <t>Cendang</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JBANG</t>
+          <t>CDANG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1192,11 +1206,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>bus A/B</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
@@ -1223,12 +1233,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bojonegoro</t>
+          <t>Jombang</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BJGRO</t>
+          <t>JBANG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1249,7 +1259,11 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>bus A/B</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
@@ -1259,14 +1273,10 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1280,12 +1290,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lamongan</t>
+          <t>Bojonegoro</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LNGAN</t>
+          <t>BJGRO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1316,10 +1326,14 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1333,12 +1347,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Holcim (KTT)</t>
+          <t>Lamongan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HOLCM</t>
+          <t>LNGAN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1359,11 +1373,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>aset milik KTT</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
@@ -1390,12 +1400,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kerek</t>
+          <t>Holcim (KTT)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KEREK</t>
+          <t>HOLCM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1416,11 +1426,15 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>aset milik KTT</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Beroperasi</t>
+          <t>Milik Pelanggan</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -1443,12 +1457,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cerme</t>
+          <t>Kerek</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CERME</t>
+          <t>KEREK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1457,7 +1471,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1469,11 +1483,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>seksi A belum energize</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
@@ -1483,14 +1493,10 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1504,12 +1510,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pucuk Ceran</t>
+          <t>Cerme</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PCRAN</t>
+          <t>CERME</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1530,7 +1536,11 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>seksi A belum energize</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
@@ -1545,7 +1555,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1561,12 +1571,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sungai Gemadu (bus 150 kV)</t>
+          <t>Pucuk Ceran</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SGMDU5</t>
+          <t>PCRAN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1575,7 +1585,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1602,7 +1612,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1618,51 +1628,33 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Sungai Gemadu</t>
+          <t>Sungai Gemadu (bus 150 kV)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IBT 1 SGMDU5</t>
+          <t>SGMDU5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>SGMDU5</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>SGMDU4</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>IBT 150/70 kV</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
@@ -1672,10 +1664,14 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1689,17 +1685,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sungai Gemadu (bus 70 kV)</t>
+          <t>IBT 150/70 kV Sungai Gemadu</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SGMDU4</t>
+          <t>IBT 1 SGMDU5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1707,15 +1703,33 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SGMDU5</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SGMDU4</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>IBT 150/70 kV</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
@@ -1742,12 +1756,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pakem Mia</t>
+          <t>Sungai Gemadu (bus 70 kV)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PKMIA</t>
+          <t>SGMDU4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1760,7 +1774,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1778,14 +1792,10 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1799,12 +1809,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Brata</t>
+          <t>Pakem Mia</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BRATA</t>
+          <t>PKMIA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1813,11 +1823,11 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1835,10 +1845,14 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1852,12 +1866,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Samsik</t>
+          <t>Brata</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SAMSIK</t>
+          <t>BRATA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1905,12 +1919,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cepu (SS Tanjung Jati)</t>
+          <t>Samsik</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CEPU</t>
+          <t>SAMSIK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1919,11 +1933,11 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1931,22 +1945,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>batas ke UP2B Jateng (SS Tanjung Jati 1,2 - Ungaran 3)</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1966,12 +1972,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Semen Tuban (KTT)</t>
+          <t>Cepu (SS Tanjung Jati)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>STBAN</t>
+          <t>CEPU</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1994,7 +2000,7 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>aset milik KTT</t>
+          <t>batas ke UP2B Jateng (SS Tanjung Jati 1,2 - Ungaran 3)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -2027,12 +2033,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tuban III (KTT)</t>
+          <t>Semen Tuban (KTT)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TUBAN3</t>
+          <t>STBAN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2061,7 +2067,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Beroperasi</t>
+          <t>Milik Pelanggan</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2081,6 +2087,67 @@
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tuban III (KTT)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TUBAN3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>aset milik KTT</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Milik Pelanggan</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3508,12 +3575,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-1-1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[N-1] Beban IBT Ngimbang akan berbeban lebih 70% apabila terjadi N- 1-1 pada PLTU Tanjung awar-awar sehingga tidak memenuhi kriteria N-1 IBT tersebut</t>
+          <t>[N-1-1] Beban IBT Ngimbang akan berbeban lebih 70% apabila terjadi N- 1-1 pada PLTU Tanjung awar-awar sehingga tidak memenuhi kriteria N-1 IBT tersebut</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3578,12 +3645,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[N-1] Busbar GI150 kVCerme dioperasikanSplit Busbar</t>
+          <t>[BELUM_DITETAPKAN] Busbar GI150 kVCerme dioperasikanSplit Busbar</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3648,12 +3715,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[N-1] Jumlah IBT 150/70 kV Segoromadu hanya ada satu kapasitas 50 MVA, sehingga apabila terjadi gangguan pada IBT tersebut maka akan terjadi pemadaman dan sulit untuk melakukan pemeliharaan</t>
+          <t>[BELUM_DITETAPKAN] Jumlah IBT 150/70 kV Segoromadu hanya ada satu kapasitas 50 MVA, sehingga apabila terjadi gangguan pada IBT tersebut maka akan terjadi pemadaman dan sulit untuk melakukan pemeliharaan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3683,12 +3750,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[N-1] Terdapat potensi ekskursi tegangan jika beban dari GI Petrokimia pada Subsistem Krian 1,2 dipindah ke Subsistem Ngimbang</t>
+          <t>[BELUM_DITETAPKAN] Terdapat potensi ekskursi tegangan jika beban dari GI Petrokimia pada Subsistem Krian 1,2 dipindah ke Subsistem Ngimbang</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3718,12 +3785,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[N-1] TerjadiDroptegangandi Subsistem Ngimbang 1,2 terutama pada saat pekerjaan di beberapa RuasPenghantar( SUTT 150 kV Babat - Lamongan-Cerme)</t>
+          <t>[BELUM_DITETAPKAN] TerjadiDroptegangandi Subsistem Ngimbang 1,2 terutama pada saat pekerjaan di beberapa RuasPenghantar( SUTT 150 kV Babat - Lamongan-Cerme)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
